--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32233-2026 artfynd.xlsx
+++ b/artfynd/A 32233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825559</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825648</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825568</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135825599</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>135825613</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>135825639</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>135825653</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135825661</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>135816279</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135816847</v>
       </c>
       <c r="B11" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
